--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,82 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,53 +744,56 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E8" s="3">
         <v>22200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,52 +806,55 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>3500</v>
       </c>
       <c r="P9" s="3">
         <v>3500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>3500</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
@@ -862,53 +868,56 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E10" s="3">
         <v>13700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +930,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,53 +956,54 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E12" s="3">
         <v>7100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>6600</v>
       </c>
       <c r="N12" s="3">
         <v>6600</v>
       </c>
       <c r="O12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="P12" s="3">
         <v>5300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5700</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1016,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,20 +1078,23 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1091,8 +1110,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1121,8 +1140,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1165,8 +1187,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1180,8 +1202,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,53 +1225,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E17" s="3">
         <v>36100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,53 +1285,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1347,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,53 +1373,54 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>39600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,53 +1433,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,28 +1495,31 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1500</v>
       </c>
       <c r="G22" s="3">
         <v>1500</v>
       </c>
       <c r="H22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1100</v>
       </c>
       <c r="J22" s="3">
         <v>1100</v>
@@ -1492,19 +1531,19 @@
         <v>1100</v>
       </c>
       <c r="M22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1518,53 +1557,56 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>30700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1619,11 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1621,8 +1666,8 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1636,8 +1681,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,53 +1743,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,53 +1805,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1867,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1929,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +1991,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2053,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,53 +2115,56 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-39600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,53 +2177,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2239,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,53 +2301,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,58 +2363,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2430,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2456,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,47 +2480,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E41" s="3">
         <v>9900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24400</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,47 +2540,50 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E42" s="3">
         <v>122000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>138300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>142900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>94000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>103900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>104600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>119700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>135000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>20000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>40000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,47 +2602,50 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E43" s="3">
         <v>15200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,47 +2664,50 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E44" s="3">
         <v>18900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,47 +2726,50 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3000</v>
       </c>
       <c r="G45" s="3">
         <v>3000</v>
       </c>
       <c r="H45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,47 +2788,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E46" s="3">
         <v>167900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>180400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>134600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>139200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>149900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>176300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>186300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>77800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2850,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2808,47 +2912,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,8 +2974,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2926,8 +3036,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3098,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,47 +3160,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1500</v>
       </c>
       <c r="G52" s="3">
         <v>1500</v>
       </c>
       <c r="H52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3222,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,47 +3284,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>182600</v>
+      </c>
+      <c r="E54" s="3">
         <v>181900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>195300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>202500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>150200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>155700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>166700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>177100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>192700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>203700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96300</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3346,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3372,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,47 +3396,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1700</v>
       </c>
       <c r="L57" s="3">
         <v>1700</v>
       </c>
       <c r="M57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3456,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3335,25 +3468,25 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3364,8 +3497,8 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3385,47 +3518,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E59" s="3">
         <v>14800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,47 +3580,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E60" s="3">
         <v>18900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,47 +3642,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>19600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>40300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>40200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>40000</v>
       </c>
       <c r="J61" s="3">
         <v>40000</v>
       </c>
       <c r="K61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="L61" s="3">
         <v>39800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>29500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3562,47 +3704,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3766,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3828,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +3890,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,47 +3952,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E66" s="3">
         <v>20400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4014,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4040,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4100,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4162,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4031,13 +4198,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>353300</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -4057,8 +4224,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,47 +4286,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-594600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-585500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-573000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-559200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-546000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-530400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-513600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-496900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-479300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-463500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-450900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-437400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4348,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4410,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4472,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,47 +4534,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E76" s="3">
         <v>161500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>157200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>145000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>96000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>110000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>123200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>138200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>150900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-313400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-301900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4596,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,58 +4658,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,53 +4725,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4787,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,8 +4813,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4625,7 +4823,7 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
@@ -4658,11 +4856,11 @@
         <v>1000</v>
       </c>
       <c r="P83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4675,8 +4873,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +4935,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +4997,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5059,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5121,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5183,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5245,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,53 +5271,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-500</v>
       </c>
       <c r="O91" s="3">
         <v>-500</v>
       </c>
       <c r="P91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5111,8 +5331,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5393,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5455,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E94" s="3">
         <v>17300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-48400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>14100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5517,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5543,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5370,8 +5603,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5665,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5727,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +5789,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>65300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>120500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,8 +5851,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5644,14 +5892,14 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5665,53 +5913,56 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +5973,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,85 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,56 +748,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E8" s="3">
         <v>28600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,55 +813,58 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2400</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3500</v>
       </c>
       <c r="Q9" s="3">
         <v>3500</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
+      <c r="R9" s="3">
+        <v>3500</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
@@ -871,56 +878,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E10" s="3">
         <v>17700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,56 +970,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>7300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>6600</v>
       </c>
       <c r="O12" s="3">
         <v>6600</v>
       </c>
       <c r="P12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>5300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5700</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,23 +1098,26 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,8 +1133,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1143,8 +1163,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1190,8 +1213,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
@@ -1205,8 +1228,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,56 +1252,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E17" s="3">
         <v>39400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,56 +1315,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,8 +1407,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1383,47 +1417,47 @@
         <v>1600</v>
       </c>
       <c r="E20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>35100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>39600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,56 +1470,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,8 +1535,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1507,22 +1547,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1500</v>
       </c>
       <c r="H22" s="3">
         <v>1500</v>
       </c>
       <c r="I22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J22" s="3">
         <v>1300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1100</v>
       </c>
       <c r="K22" s="3">
         <v>1100</v>
@@ -1534,19 +1574,19 @@
         <v>1100</v>
       </c>
       <c r="N22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1560,56 +1600,59 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>30700</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,8 +1665,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1669,8 +1715,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1684,8 +1730,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,56 +1795,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30700</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,56 +1860,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,8 +2185,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2127,47 +2197,47 @@
         <v>-1600</v>
       </c>
       <c r="E32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-39600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,56 +2250,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,56 +2380,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,61 +2445,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,50 +2567,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,50 +2630,53 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E42" s="3">
         <v>117500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>122000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>138300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>142900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>94000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>103900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>104600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>119700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>135000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>100000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>40000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,50 +2695,53 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E43" s="3">
         <v>20300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,50 +2760,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E44" s="3">
         <v>17400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>15300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,50 +2825,53 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3000</v>
       </c>
       <c r="H45" s="3">
         <v>3000</v>
       </c>
       <c r="I45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,50 +2890,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E46" s="3">
         <v>168400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>167900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>180400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>187700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>134600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>149900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>176300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>186300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>77800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +2955,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2915,50 +3020,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E48" s="3">
         <v>13300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,8 +3085,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3039,8 +3150,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3280,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3172,41 +3292,41 @@
         <v>900</v>
       </c>
       <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1500</v>
       </c>
       <c r="H52" s="3">
         <v>1500</v>
       </c>
       <c r="I52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,50 +3410,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>183200</v>
+      </c>
+      <c r="E54" s="3">
         <v>182600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>181900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>195300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>202500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>150200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>155700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>166700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>177100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>192700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>203700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,50 +3527,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1700</v>
       </c>
       <c r="M57" s="3">
         <v>1700</v>
       </c>
       <c r="N57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,8 +3590,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3471,25 +3605,25 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3500,8 +3634,8 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3521,50 +3655,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E59" s="3">
         <v>17000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,50 +3720,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E60" s="3">
         <v>20900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3785,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3654,41 +3797,41 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>19600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>40300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>40000</v>
       </c>
       <c r="K61" s="3">
         <v>40000</v>
       </c>
       <c r="L61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="M61" s="3">
         <v>39800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>29500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3707,50 +3850,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,50 +4110,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E66" s="3">
         <v>22200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>56700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>44900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4201,13 +4369,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>353300</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,50 +4460,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-603700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-594600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-585500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-573000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-559200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-546000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-530400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-513600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-496900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-479300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-463500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-450900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-437400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,50 +4720,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E76" s="3">
         <v>160400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>157200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>145000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>96000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>110000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>123200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>138200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>150900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-313400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-301900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,61 +4850,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,56 +4920,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,8 +5012,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,7 +5025,7 @@
         <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -4859,11 +5058,11 @@
         <v>1000</v>
       </c>
       <c r="Q83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,56 +5400,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,56 +5492,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-500</v>
       </c>
       <c r="P91" s="3">
         <v>-500</v>
       </c>
       <c r="Q91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5334,8 +5555,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,56 +5685,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E94" s="3">
         <v>4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-48400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-80200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5750,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,56 +6035,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>65300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>120500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5895,14 +6144,14 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -5916,56 +6165,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-43700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,59 +752,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E8" s="3">
         <v>29500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,58 +820,61 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>3500</v>
       </c>
       <c r="R9" s="3">
         <v>3500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>3500</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
@@ -881,59 +888,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E10" s="3">
         <v>20700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,59 +984,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E12" s="3">
         <v>8000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>6600</v>
       </c>
       <c r="P12" s="3">
         <v>6600</v>
       </c>
       <c r="Q12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="R12" s="3">
         <v>5300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5700</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,26 +1118,29 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1136,8 +1156,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1166,8 +1186,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1216,8 +1239,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1231,8 +1254,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,59 +1279,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E17" s="3">
         <v>40200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,59 +1345,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,59 +1441,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
       <c r="E20" s="3">
         <v>1600</v>
       </c>
       <c r="F20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>35100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>39600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1473,59 +1507,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,8 +1575,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,22 +1590,22 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1500</v>
       </c>
       <c r="I22" s="3">
         <v>1500</v>
       </c>
       <c r="J22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K22" s="3">
         <v>1300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1100</v>
       </c>
       <c r="L22" s="3">
         <v>1100</v>
@@ -1577,19 +1617,19 @@
         <v>1100</v>
       </c>
       <c r="O22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1603,59 +1643,62 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>30700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,8 +1711,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1718,8 +1764,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1733,8 +1779,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,59 +1847,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,59 +1915,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,59 +2255,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1600</v>
+        <v>-2300</v>
       </c>
       <c r="E32" s="3">
         <v>-1600</v>
       </c>
       <c r="F32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-35100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-39600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,59 +2323,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,59 +2459,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,64 +2527,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,53 +2654,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E41" s="3">
         <v>32600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2633,53 +2720,56 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>208800</v>
+      </c>
+      <c r="E42" s="3">
         <v>92700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>117500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>122000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>138300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>142900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>94000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>103900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>104600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>119700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>135000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>40000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,53 +2788,56 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E43" s="3">
         <v>21600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,53 +2856,56 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E44" s="3">
         <v>18700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>15300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2828,53 +2924,56 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>3000</v>
       </c>
       <c r="I45" s="3">
         <v>3000</v>
       </c>
       <c r="J45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,53 +2992,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E46" s="3">
         <v>168600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>168400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>167900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>180400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>187700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>134600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>139200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>149900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>161100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>176300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>186300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>75500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>77800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3060,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3023,53 +3128,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3088,8 +3196,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3153,8 +3264,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,53 +3400,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
         <v>900</v>
       </c>
       <c r="F52" s="3">
+        <v>900</v>
+      </c>
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1500</v>
       </c>
       <c r="I52" s="3">
         <v>1500</v>
       </c>
       <c r="J52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,53 +3536,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>305500</v>
+      </c>
+      <c r="E54" s="3">
         <v>183200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>182600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>181900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>195300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>202500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>150200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>155700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>166700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>177100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>192700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>203700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>96300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,8 +3658,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3537,44 +3668,44 @@
         <v>5100</v>
       </c>
       <c r="E57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1700</v>
       </c>
       <c r="N57" s="3">
         <v>1700</v>
       </c>
       <c r="O57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P57" s="3">
         <v>2300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,8 +3724,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3608,25 +3742,25 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3637,8 +3771,8 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3658,53 +3792,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E59" s="3">
         <v>13200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,53 +3860,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E60" s="3">
         <v>18300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,8 +3928,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3800,41 +3943,41 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>19600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>40300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>40000</v>
       </c>
       <c r="L61" s="3">
         <v>40000</v>
       </c>
       <c r="M61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="N61" s="3">
         <v>39800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>39700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>29500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3853,53 +3996,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3918,8 +4064,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,53 +4268,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E66" s="3">
         <v>19200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>56700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>44900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4372,13 +4540,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>353300</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,53 +4634,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-609800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-603700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-594600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-585500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-573000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-559200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-546000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-530400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-513600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-496900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-479300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-463500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-450900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-437400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,53 +4906,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E76" s="3">
         <v>163900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>160400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>157200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>145000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>96000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>110000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>123200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>138200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>150900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-313400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-301900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,64 +5042,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,59 +5115,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,13 +5211,14 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -5028,7 +5227,7 @@
         <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
@@ -5061,11 +5260,11 @@
         <v>1000</v>
       </c>
       <c r="R83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,59 +5617,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,59 +5713,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-400</v>
       </c>
       <c r="M91" s="3">
         <v>-400</v>
       </c>
       <c r="N91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-500</v>
       </c>
       <c r="Q91" s="3">
         <v>-500</v>
       </c>
       <c r="R91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5558,8 +5779,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,59 +5915,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115600</v>
+      </c>
+      <c r="E94" s="3">
         <v>24300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-48400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-80200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5753,8 +5983,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,8 +6011,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,59 +6281,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E100" s="3">
         <v>8000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>65300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>120500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>24300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,8 +6349,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6147,14 +6396,14 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6168,59 +6417,62 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E102" s="3">
         <v>23000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-43700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,62 +756,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E8" s="3">
         <v>34900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,61 +827,64 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E9" s="3">
         <v>10600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2400</v>
-      </c>
-      <c r="R9" s="3">
-        <v>3500</v>
       </c>
       <c r="S9" s="3">
         <v>3500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="T9" s="3">
+        <v>3500</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
@@ -891,62 +898,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E10" s="3">
         <v>24300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,62 +998,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E12" s="3">
         <v>8300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7100</v>
       </c>
-      <c r="H12" s="3">
-        <v>7300</v>
-      </c>
       <c r="I12" s="3">
-        <v>7100</v>
+        <v>7400</v>
       </c>
       <c r="J12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K12" s="3">
         <v>6600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>6600</v>
       </c>
       <c r="Q12" s="3">
         <v>6600</v>
       </c>
       <c r="R12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="S12" s="3">
         <v>5300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5700</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,29 +1138,32 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1159,8 +1179,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1189,31 +1209,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1242,8 +1265,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,62 +1306,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E17" s="3">
         <v>43200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39400</v>
       </c>
-      <c r="G17" s="3">
-        <v>36100</v>
-      </c>
       <c r="H17" s="3">
-        <v>34800</v>
+        <v>34700</v>
       </c>
       <c r="I17" s="3">
+        <v>34400</v>
+      </c>
+      <c r="J17" s="3">
         <v>30600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,62 +1375,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-10800</v>
-      </c>
       <c r="G18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-15800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-13900</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,62 +1475,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>35100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>39600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,62 +1544,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5200</v>
+        <v>-8100</v>
       </c>
       <c r="E21" s="3">
-        <v>-7900</v>
+        <v>-7500</v>
       </c>
       <c r="F21" s="3">
-        <v>-8100</v>
+        <v>-9600</v>
       </c>
       <c r="G21" s="3">
-        <v>-11000</v>
+        <v>-9800</v>
       </c>
       <c r="H21" s="3">
-        <v>-11200</v>
+        <v>-11400</v>
       </c>
       <c r="I21" s="3">
-        <v>-10700</v>
+        <v>-12600</v>
       </c>
       <c r="J21" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-13200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1615,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1593,22 +1633,22 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1500</v>
       </c>
       <c r="J22" s="3">
         <v>1500</v>
       </c>
       <c r="K22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L22" s="3">
         <v>1300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1100</v>
       </c>
       <c r="M22" s="3">
         <v>1100</v>
@@ -1620,19 +1660,19 @@
         <v>1100</v>
       </c>
       <c r="P22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1646,62 +1686,65 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>30700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1757,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1737,8 +1783,8 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1767,8 +1813,8 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1899,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30700</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +1970,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,62 +2325,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-35100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-39600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,62 +2396,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2538,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,56 +2741,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E41" s="3">
         <v>24400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,56 +2810,59 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E42" s="3">
         <v>208800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>117500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>122000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>138300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>142900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>94000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>103900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>104600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>119700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>135000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>40000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,56 +2881,59 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E43" s="3">
         <v>25700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,56 +2952,59 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E44" s="3">
         <v>19400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9800</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,56 +3023,59 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="E45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,56 +3094,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>286800</v>
+      </c>
+      <c r="E46" s="3">
         <v>281200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>168600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>168400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>167900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>180400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>187700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>134600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>139200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>149900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>176300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>186300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>75500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>77800</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,31 +3165,34 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3131,56 +3236,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E48" s="3">
         <v>23300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,8 +3307,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,56 +3520,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>900</v>
       </c>
       <c r="F52" s="3">
         <v>900</v>
       </c>
       <c r="G52" s="3">
+        <v>900</v>
+      </c>
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1500</v>
       </c>
       <c r="K52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,56 +3662,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>310500</v>
+      </c>
+      <c r="E54" s="3">
         <v>305500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>183200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>182600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>181900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>195300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>202500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>150200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>155700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>166700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>177100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>192700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>203700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>96300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,56 +3789,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5100</v>
+        <v>4600</v>
       </c>
       <c r="E57" s="3">
         <v>5100</v>
       </c>
       <c r="F57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1700</v>
       </c>
       <c r="O57" s="3">
         <v>1700</v>
       </c>
       <c r="P57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,43 +3858,46 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3774,8 +3908,8 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3795,56 +3929,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>14500</v>
       </c>
-      <c r="E59" s="3">
-        <v>13200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>17000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>14800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>12500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>14500</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,56 +4000,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E60" s="3">
         <v>19600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,56 +4071,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>10600</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>10700</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H61" s="3">
-        <v>19600</v>
+        <v>1400</v>
       </c>
       <c r="I61" s="3">
-        <v>40300</v>
+        <v>21400</v>
       </c>
       <c r="J61" s="3">
+        <v>42600</v>
+      </c>
+      <c r="K61" s="3">
         <v>40200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>40000</v>
       </c>
       <c r="M61" s="3">
         <v>40000</v>
       </c>
       <c r="N61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="O61" s="3">
         <v>39800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>39500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>29500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3999,56 +4142,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1200</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,56 +4426,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E66" s="3">
         <v>30300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>60300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>56700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>44900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4543,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>353300</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,56 +4808,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-616200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-609800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-603700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-594600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-585500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-573000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-559200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-546000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-530400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-513600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-496900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-479300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-463500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-450900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-437400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,56 +5092,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E76" s="3">
         <v>275200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>163900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>160400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>161500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>157200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>145000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>89900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>96000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>110000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>123200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>138200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>150900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-313400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-301900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5310,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,22 +5410,23 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
@@ -5263,11 +5462,11 @@
         <v>1000</v>
       </c>
       <c r="S83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,62 +5834,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,62 +5934,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-400</v>
       </c>
       <c r="N91" s="3">
         <v>-400</v>
       </c>
       <c r="O91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
       <c r="S91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,62 +6145,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-115600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>17300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-48400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-80200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>14500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>6400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,31 +6245,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>111500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>65300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>120500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,8 +6598,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6399,14 +6648,14 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -6420,62 +6669,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,97 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,65 +759,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E8" s="3">
         <v>35300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,64 +833,67 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E9" s="3">
         <v>10100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2400</v>
-      </c>
-      <c r="S9" s="3">
-        <v>3500</v>
       </c>
       <c r="T9" s="3">
         <v>3500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3">
+        <v>3500</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
@@ -901,65 +907,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E10" s="3">
         <v>25200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,65 +1011,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E12" s="3">
         <v>8800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>6600</v>
       </c>
       <c r="R12" s="3">
         <v>6600</v>
       </c>
       <c r="S12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="T12" s="3">
         <v>5300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5700</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1157,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1155,18 +1174,18 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1182,8 +1201,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1212,19 +1231,22 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1100</v>
       </c>
       <c r="G15" s="3">
         <v>1100</v>
@@ -1233,13 +1255,13 @@
         <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1268,8 +1290,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
@@ -1283,8 +1305,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,65 +1332,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E17" s="3">
         <v>44500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,65 +1404,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1478,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,8 +1508,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1502,39 +1535,39 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>35100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1580,11 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1556,56 +1592,56 @@
         <v>-8100</v>
       </c>
       <c r="E21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,8 +1654,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1636,22 +1675,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1500</v>
       </c>
       <c r="K22" s="3">
         <v>1500</v>
       </c>
       <c r="L22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M22" s="3">
         <v>1300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1100</v>
       </c>
       <c r="N22" s="3">
         <v>1100</v>
@@ -1663,19 +1702,19 @@
         <v>1100</v>
       </c>
       <c r="Q22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1689,65 +1728,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>26300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>30700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1802,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1783,11 +1828,11 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1816,8 +1861,8 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1831,8 +1876,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,65 +1950,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30700</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,65 +2024,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2098,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2172,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2246,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,8 +2394,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2354,39 +2423,39 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-35100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,65 +2468,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2542,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,65 +2616,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2690,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2769,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,8 +2827,9 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2751,50 +2837,50 @@
         <v>16700</v>
       </c>
       <c r="E41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F41" s="3">
         <v>24400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,59 +2899,62 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>220500</v>
+      </c>
+      <c r="E42" s="3">
         <v>220400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>208800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>117500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>122000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>138300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>142900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>94000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>103900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>104600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>119700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>135000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>20000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>40000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,59 +2973,62 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E43" s="3">
         <v>25400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2300</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,59 +3047,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E44" s="3">
         <v>21700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3121,11 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3052,33 +3150,33 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,59 +3195,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E46" s="3">
         <v>286800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>281200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>168600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>168400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>167900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>180400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>187700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>134600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>139200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>149900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>161100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>176300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>186300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>75500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>77800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3269,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3194,8 +3298,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3239,59 +3343,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E48" s="3">
         <v>22800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,8 +3417,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3381,8 +3491,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,59 +3639,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>900</v>
       </c>
       <c r="G52" s="3">
         <v>900</v>
       </c>
       <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1500</v>
       </c>
       <c r="K52" s="3">
         <v>1500</v>
       </c>
       <c r="L52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>900</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3713,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,59 +3787,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>318600</v>
+      </c>
+      <c r="E54" s="3">
         <v>310500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>305500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>183200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>182600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>181900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>195300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>202500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>150200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>155700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>166700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>177100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>192700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>203700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>94900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>96300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3861,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,59 +3919,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>5100</v>
       </c>
       <c r="F57" s="3">
         <v>5100</v>
       </c>
       <c r="G57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1700</v>
       </c>
       <c r="P57" s="3">
         <v>1700</v>
       </c>
       <c r="Q57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R57" s="3">
         <v>2300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,25 +3991,28 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
       </c>
       <c r="F58" s="3">
+        <v>700</v>
+      </c>
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
@@ -3888,19 +4021,19 @@
         <v>2000</v>
       </c>
       <c r="K58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="L58" s="3">
         <v>200</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3911,8 +4044,8 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3932,13 +4065,16 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>5900</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -3946,45 +4082,45 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>14500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,59 +4139,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E60" s="3">
         <v>22600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,59 +4213,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E61" s="3">
         <v>10600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>40000</v>
       </c>
       <c r="N61" s="3">
         <v>40000</v>
       </c>
       <c r="O61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="P61" s="3">
         <v>39800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>39700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>39500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>29500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4145,13 +4287,16 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>100</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
@@ -4159,8 +4304,8 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>100</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -4168,36 +4313,36 @@
       <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4361,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,59 +4583,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E66" s="3">
         <v>33200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>60300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>56700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>54500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>44900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4657,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4714,13 +4881,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>353300</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4740,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,59 +4981,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-622100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-616200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-609800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-603700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-594600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-585500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-573000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-559200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-546000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-530400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-513600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-496900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-479300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-463500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-450900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-437400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5055,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,59 +5277,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>281200</v>
+      </c>
+      <c r="E76" s="3">
         <v>277300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>275200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>163900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>160400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>157200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>145000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>96000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>110000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>123200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>138200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>150900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-313400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-301900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5351,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5425,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,65 +5504,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5578,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,8 +5608,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5420,7 +5618,7 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
@@ -5465,11 +5663,11 @@
         <v>1000</v>
       </c>
       <c r="T83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U83" s="3">
         <v>1100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5680,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6050,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6124,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,65 +6154,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-400</v>
       </c>
       <c r="O91" s="3">
         <v>-400</v>
       </c>
       <c r="P91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-500</v>
       </c>
       <c r="S91" s="3">
         <v>-500</v>
       </c>
       <c r="T91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6006,8 +6226,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,65 +6374,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-80200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>19200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>14500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>6400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6448,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6478,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6272,8 +6505,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6317,8 +6550,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6772,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>111500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>65300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>120500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,8 +6846,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6651,14 +6899,14 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6672,65 +6920,68 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6992,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,100 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -762,68 +763,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E8" s="3">
         <v>40200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -836,67 +840,70 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
         <v>11400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2400</v>
-      </c>
-      <c r="T9" s="3">
-        <v>3500</v>
       </c>
       <c r="U9" s="3">
         <v>3500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
+      <c r="V9" s="3">
+        <v>3500</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
@@ -910,68 +917,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E10" s="3">
         <v>28800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,68 +1025,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E12" s="3">
         <v>9200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5300</v>
-      </c>
-      <c r="R12" s="3">
-        <v>6600</v>
       </c>
       <c r="S12" s="3">
         <v>6600</v>
       </c>
       <c r="T12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U12" s="3">
         <v>5300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5700</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,8 +1177,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1177,18 +1197,18 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1204,8 +1224,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1234,22 +1254,25 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1100</v>
       </c>
       <c r="H15" s="3">
         <v>1100</v>
@@ -1258,13 +1281,13 @@
         <v>1100</v>
       </c>
       <c r="J15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1293,8 +1316,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
@@ -1308,8 +1331,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,68 +1359,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E17" s="3">
         <v>48800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,68 +1434,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1511,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,8 +1542,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1538,39 +1572,39 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>35100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,68 +1617,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8100</v>
+        <v>-9900</v>
       </c>
       <c r="E21" s="3">
         <v>-8100</v>
       </c>
       <c r="F21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-14500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>31800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,8 +1694,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1678,22 +1718,22 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1500</v>
       </c>
       <c r="L22" s="3">
         <v>1500</v>
       </c>
       <c r="M22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N22" s="3">
         <v>1300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1100</v>
       </c>
       <c r="O22" s="3">
         <v>1100</v>
@@ -1705,19 +1745,19 @@
         <v>1100</v>
       </c>
       <c r="R22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1731,68 +1771,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>26300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30700</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,8 +1848,11 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1831,11 +1877,11 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1864,8 +1910,8 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1879,8 +1925,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,68 +2002,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>30700</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,68 +2079,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2101,8 +2156,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2249,8 +2310,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,8 +2464,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2426,39 +2496,39 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-35100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,68 +2541,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2618,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,68 +2695,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,73 +2772,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2854,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,62 +2914,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16700</v>
+        <v>28000</v>
       </c>
       <c r="E41" s="3">
         <v>16700</v>
       </c>
       <c r="F41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="G41" s="3">
         <v>24400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,62 +2989,65 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>201300</v>
+      </c>
+      <c r="E42" s="3">
         <v>220500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>220400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>208800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>117500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>122000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>138300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>142900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>94000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>103900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>104600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>119700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>135000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>100000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>40000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,62 +3066,65 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E43" s="3">
         <v>30100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3050,62 +3143,65 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E44" s="3">
         <v>22000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>19400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9800</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3124,8 +3220,11 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3153,33 +3252,33 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,62 +3297,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E46" s="3">
         <v>293800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>286800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>281200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>168600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>168400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>167900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>180400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>187700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>134600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>149900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>161100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>176300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>186300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>75500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>77800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3272,8 +3374,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3301,8 +3406,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3346,62 +3451,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E48" s="3">
         <v>23600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3420,8 +3528,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3494,8 +3605,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,62 +3759,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>900</v>
       </c>
       <c r="H52" s="3">
         <v>900</v>
       </c>
       <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1500</v>
       </c>
       <c r="L52" s="3">
         <v>1500</v>
       </c>
       <c r="M52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>900</v>
       </c>
       <c r="P52" s="3">
         <v>900</v>
       </c>
       <c r="Q52" s="3">
+        <v>900</v>
+      </c>
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3716,8 +3836,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,62 +3913,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E54" s="3">
         <v>318600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>310500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>305500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>183200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>182600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>181900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>195300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>202500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>150200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>155700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>166700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>177100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>192700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>203700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>94900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>96300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3990,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,62 +4050,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E57" s="3">
         <v>4500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>5100</v>
       </c>
       <c r="G57" s="3">
         <v>5100</v>
       </c>
       <c r="H57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1700</v>
       </c>
       <c r="Q57" s="3">
         <v>1700</v>
       </c>
       <c r="R57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S57" s="3">
         <v>2300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,28 +4125,31 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>700</v>
       </c>
       <c r="G58" s="3">
+        <v>700</v>
+      </c>
+      <c r="H58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1800</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
@@ -4024,19 +4158,19 @@
         <v>2000</v>
       </c>
       <c r="L58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4047,8 +4181,8 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4068,62 +4202,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>14500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4142,62 +4279,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E60" s="3">
         <v>25900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,62 +4356,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40100</v>
-      </c>
-      <c r="N61" s="3">
-        <v>40000</v>
       </c>
       <c r="O61" s="3">
         <v>40000</v>
       </c>
       <c r="P61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>39800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>39700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>39500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4290,25 +4433,28 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
-        <v>100</v>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
@@ -4316,36 +4462,36 @@
       <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4364,8 +4510,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,62 +4741,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E66" s="3">
         <v>37300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4818,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4884,13 +5052,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>353300</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4910,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,62 +5155,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-630300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-622100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-616200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-609800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-603700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-594600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-585500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-573000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-559200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-546000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-530400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-513600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-496900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-479300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-463500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-450900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-437400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5058,8 +5232,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,62 +5463,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>279300</v>
+      </c>
+      <c r="E76" s="3">
         <v>281200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>277300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>163900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>160400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>161500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>157200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>145000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>89900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>96000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>110000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>123200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>150900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-313400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-301900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5354,8 +5540,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,73 +5617,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5507,68 +5699,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5581,8 +5776,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,8 +5807,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5621,7 +5820,7 @@
         <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -5666,11 +5865,11 @@
         <v>1000</v>
       </c>
       <c r="U83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V83" s="3">
         <v>1100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5683,8 +5882,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,68 +6267,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6127,8 +6344,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,68 +6375,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-400</v>
       </c>
       <c r="P91" s="3">
         <v>-400</v>
       </c>
       <c r="Q91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-500</v>
       </c>
       <c r="T91" s="3">
         <v>-500</v>
       </c>
       <c r="U91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6229,8 +6450,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,68 +6604,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E94" s="3">
         <v>1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-115600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>17300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-48400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>10400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-80200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>14500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>6400</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6451,8 +6681,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,8 +6712,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6508,8 +6742,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6553,8 +6787,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,68 +7018,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>111500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>65300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>120500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>10200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>24300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6849,8 +7095,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6902,14 +7151,14 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -6923,68 +7172,71 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-7700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>23000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,6 +7247,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,104 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -766,71 +767,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E8" s="3">
         <v>37900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,70 +847,73 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E9" s="3">
         <v>9600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2400</v>
-      </c>
-      <c r="U9" s="3">
-        <v>3500</v>
       </c>
       <c r="V9" s="3">
         <v>3500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
+      <c r="W9" s="3">
+        <v>3500</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
@@ -920,71 +927,74 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E10" s="3">
         <v>28300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>17700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -997,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1026,71 +1039,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E12" s="3">
         <v>10400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5300</v>
-      </c>
-      <c r="S12" s="3">
-        <v>6600</v>
       </c>
       <c r="T12" s="3">
         <v>6600</v>
       </c>
       <c r="U12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V12" s="3">
         <v>5300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5700</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1103,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1180,8 +1197,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1200,18 +1220,18 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,8 +1247,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1257,8 +1277,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1266,16 +1289,16 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
+        <v>800</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1100</v>
       </c>
       <c r="I15" s="3">
         <v>1100</v>
@@ -1284,13 +1307,13 @@
         <v>1100</v>
       </c>
       <c r="K15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="L15" s="3">
         <v>1000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1319,8 +1342,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
@@ -1334,8 +1357,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1360,71 +1386,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E17" s="3">
         <v>48600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>43200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,71 +1464,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1514,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1543,8 +1576,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1575,39 +1609,39 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,71 +1654,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-8100</v>
       </c>
       <c r="F21" s="3">
         <v>-8100</v>
       </c>
       <c r="G21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>31800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,8 +1734,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1721,22 +1761,22 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1500</v>
       </c>
       <c r="M22" s="3">
         <v>1500</v>
       </c>
       <c r="N22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O22" s="3">
         <v>1300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1100</v>
       </c>
       <c r="P22" s="3">
         <v>1100</v>
@@ -1748,19 +1788,19 @@
         <v>1100</v>
       </c>
       <c r="S22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1774,71 +1814,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>26300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>30700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1851,8 +1894,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1880,11 +1926,11 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1913,8 +1959,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1928,8 +1974,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2005,71 +2054,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30700</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,71 +2134,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5900</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2159,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2236,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2313,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2390,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,8 +2534,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2499,39 +2569,39 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,71 +2614,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2621,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2698,71 +2774,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2775,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2886,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2915,65 +3001,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E41" s="3">
         <v>28000</v>
-      </c>
-      <c r="E41" s="3">
-        <v>16700</v>
       </c>
       <c r="F41" s="3">
         <v>16700</v>
       </c>
       <c r="G41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="H41" s="3">
         <v>24400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>32600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>68300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2992,65 +3079,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E42" s="3">
         <v>201300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>220500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>220400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>208800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>117500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>122000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>138300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>142900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>94000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>103900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>104600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>119700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>135000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>100000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>40000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3069,65 +3159,68 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E43" s="3">
         <v>31000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2300</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3146,65 +3239,68 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E44" s="3">
         <v>23600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>22000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9800</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3319,11 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3255,33 +3354,33 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3300,65 +3399,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E46" s="3">
         <v>288400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>293800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>286800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>281200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>168600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>168400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>167900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>180400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>187700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>134600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>139200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>149900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>161100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>176300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>186300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>75500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>77800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3479,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3409,8 +3514,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3454,65 +3559,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E48" s="3">
         <v>23500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3639,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3608,8 +3719,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3685,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3762,65 +3879,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>900</v>
       </c>
       <c r="I52" s="3">
         <v>900</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
       </c>
       <c r="N52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O52" s="3">
         <v>1600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>900</v>
       </c>
       <c r="Q52" s="3">
         <v>900</v>
       </c>
       <c r="R52" s="3">
+        <v>900</v>
+      </c>
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3916,65 +4039,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>309000</v>
+      </c>
+      <c r="E54" s="3">
         <v>313000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>318600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>310500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>305500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>183200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>181900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>195300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>202500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>150200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>155700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>166700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>177100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>192700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>203700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>94900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>96300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4022,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4051,65 +4181,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5100</v>
       </c>
       <c r="H57" s="3">
         <v>5100</v>
       </c>
       <c r="I57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1700</v>
       </c>
       <c r="R57" s="3">
         <v>1700</v>
       </c>
       <c r="S57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4128,8 +4259,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4137,22 +4271,22 @@
         <v>1100</v>
       </c>
       <c r="E58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>700</v>
       </c>
       <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
         <v>1600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
@@ -4161,19 +4295,19 @@
         <v>2000</v>
       </c>
       <c r="M58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4184,8 +4318,8 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4205,65 +4339,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>5900</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>14500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,65 +4419,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E60" s="3">
         <v>22700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,65 +4499,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E61" s="3">
         <v>11000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40100</v>
-      </c>
-      <c r="O61" s="3">
-        <v>40000</v>
       </c>
       <c r="P61" s="3">
         <v>40000</v>
       </c>
       <c r="Q61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="R61" s="3">
         <v>39800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>39700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4436,28 +4579,31 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>100</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
@@ -4465,36 +4611,36 @@
       <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4513,8 +4659,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4590,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4667,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4744,65 +4899,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>44900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4850,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4927,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5004,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5055,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>353300</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -5081,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5158,65 +5329,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-642100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-630300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-622100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-616200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-609800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-603700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-594600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-585500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-573000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-559200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-546000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-530400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-513600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-496900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-479300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-463500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-450900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-437400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5235,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5312,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5389,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5466,65 +5649,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E76" s="3">
         <v>279300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>281200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>277300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>163900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>161500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>157200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>145000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>96000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>110000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>123200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>138200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>150900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-313400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-301900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5543,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5620,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5702,71 +5894,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5779,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5808,13 +6006,14 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -5823,7 +6022,7 @@
         <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
@@ -5868,11 +6067,11 @@
         <v>1000</v>
       </c>
       <c r="V83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W83" s="3">
         <v>1100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5885,8 +6084,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5962,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6039,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6116,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6193,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6270,71 +6484,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6347,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6376,71 +6596,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-400</v>
       </c>
       <c r="Q91" s="3">
         <v>-400</v>
       </c>
       <c r="R91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-500</v>
       </c>
       <c r="U91" s="3">
         <v>-500</v>
       </c>
       <c r="V91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6453,8 +6674,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6530,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6607,71 +6834,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E94" s="3">
         <v>20900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-115600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>17300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-48400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-80200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>19200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>14500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>6400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6684,8 +6914,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6713,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6790,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6867,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6944,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7021,71 +7264,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>111500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>65300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>120500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>10200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>24300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7098,8 +7344,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7154,14 +7403,14 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -7175,71 +7424,74 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E102" s="3">
         <v>11300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-7700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>23000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-43700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>26500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7250,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,112 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,77 +774,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E8" s="3">
         <v>30300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>40200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,76 +860,79 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E9" s="3">
         <v>6100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2400</v>
-      </c>
-      <c r="W9" s="3">
-        <v>3500</v>
       </c>
       <c r="X9" s="3">
         <v>3500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
+      <c r="Y9" s="3">
+        <v>3500</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
@@ -940,77 +946,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E10" s="3">
         <v>24200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1032,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,77 +1066,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E12" s="3">
         <v>9100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10400</v>
       </c>
-      <c r="G12" s="3">
-        <v>9200</v>
-      </c>
       <c r="H12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I12" s="3">
         <v>8800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5300</v>
-      </c>
-      <c r="U12" s="3">
-        <v>6600</v>
       </c>
       <c r="V12" s="3">
         <v>6600</v>
       </c>
       <c r="W12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="X12" s="3">
         <v>5300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5700</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1150,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,8 +1236,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1246,18 +1265,18 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1273,8 +1292,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1303,8 +1322,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,22 +1334,22 @@
         <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
       </c>
       <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1100</v>
       </c>
       <c r="K15" s="3">
         <v>1100</v>
@@ -1336,13 +1358,13 @@
         <v>1100</v>
       </c>
       <c r="M15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="N15" s="3">
         <v>1000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1371,8 +1393,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
@@ -1386,8 +1408,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,77 +1439,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E17" s="3">
         <v>42500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,77 +1523,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1609,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,8 +1643,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1649,39 +1682,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>35100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>39600</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,77 +1727,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-8100</v>
       </c>
       <c r="H21" s="3">
         <v>-8100</v>
       </c>
       <c r="I21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-13600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-11700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>27800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>31800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,8 +1813,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1807,22 +1846,22 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1500</v>
       </c>
       <c r="O22" s="3">
         <v>1500</v>
       </c>
       <c r="P22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1100</v>
       </c>
       <c r="R22" s="3">
         <v>1100</v>
@@ -1834,19 +1873,19 @@
         <v>1100</v>
       </c>
       <c r="U22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1860,77 +1899,80 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>30700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,8 +1985,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1978,11 +2023,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2011,8 +2056,8 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -2026,8 +2071,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,77 +2157,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>30700</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,77 +2243,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2329,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2415,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,8 +2501,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2587,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,8 +2673,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2645,39 +2714,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-35100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-39600</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,77 +2759,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2845,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,77 +2931,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,82 +3017,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3108,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3142,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,71 +3174,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E41" s="3">
         <v>29600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>16700</v>
       </c>
       <c r="H41" s="3">
         <v>16700</v>
       </c>
       <c r="I41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J41" s="3">
         <v>24400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>41700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,71 +3258,74 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>208200</v>
+      </c>
+      <c r="E42" s="3">
         <v>197900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>187100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>201300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>220500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>220400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>208800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>117500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>122000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>138300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>142900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>94000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>103900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>104600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>119700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>135000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>100000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>20000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>40000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3255,71 +3344,74 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E43" s="3">
         <v>24200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2300</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,71 +3430,74 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E44" s="3">
         <v>29000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>22000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>15300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>9800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,8 +3516,11 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3459,33 +3557,33 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,71 +3602,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>283900</v>
+        <v>287500</v>
       </c>
       <c r="E46" s="3">
         <v>283900</v>
       </c>
       <c r="F46" s="3">
+        <v>283900</v>
+      </c>
+      <c r="G46" s="3">
         <v>288400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>293800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>286800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>281200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>168600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>168400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>167900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>180400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>187700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>134600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>139200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>149900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>161100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>176300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>186300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>75500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>77800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,8 +3688,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3625,8 +3729,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3670,71 +3774,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3753,8 +3860,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3836,8 +3946,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4032,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,8 +4118,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4014,59 +4133,59 @@
         <v>1300</v>
       </c>
       <c r="F52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>1500</v>
       </c>
       <c r="P52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>900</v>
       </c>
       <c r="S52" s="3">
         <v>900</v>
       </c>
       <c r="T52" s="3">
+        <v>900</v>
+      </c>
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4204,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,71 +4290,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>311800</v>
+      </c>
+      <c r="E54" s="3">
         <v>308500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>309000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>313000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>318600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>310500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>305500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>183200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>181900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>195300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>202500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>150200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>155700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>166700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>192700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>203700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>94900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>96300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4376,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4410,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,71 +4442,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5100</v>
       </c>
       <c r="J57" s="3">
         <v>5100</v>
       </c>
       <c r="K57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1700</v>
       </c>
       <c r="T57" s="3">
         <v>1700</v>
       </c>
       <c r="U57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,37 +4526,40 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1100</v>
       </c>
       <c r="F58" s="3">
         <v>1100</v>
       </c>
       <c r="G58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H58" s="3">
         <v>1000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>700</v>
       </c>
       <c r="J58" s="3">
+        <v>700</v>
+      </c>
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>2000</v>
@@ -4435,19 +4568,19 @@
         <v>2000</v>
       </c>
       <c r="O58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="P58" s="3">
         <v>200</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4458,8 +4591,8 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4479,13 +4612,16 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>9300</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -4493,57 +4629,57 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>5900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>4600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>14500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4562,71 +4698,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E60" s="3">
         <v>22300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,71 +4784,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E61" s="3">
         <v>10300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>40100</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>40000</v>
       </c>
       <c r="R61" s="3">
         <v>40000</v>
       </c>
       <c r="S61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="T61" s="3">
         <v>39800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>39700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4728,8 +4870,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4742,20 +4887,20 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>100</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
@@ -4763,36 +4908,36 @@
       <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="N62" s="3">
+        <v>100</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +4956,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5042,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5128,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,71 +5214,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E66" s="3">
         <v>32600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>56700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>54500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>52800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>44900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5143,8 +5300,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5334,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5418,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,8 +5504,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5397,13 +5564,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>353300</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5423,8 +5590,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,71 +5676,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-661000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-651900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-642100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-630300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-622100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-616200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-609800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-603700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-594600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-585500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-573000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-559200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-546000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-530400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-513600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-496900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-479300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-463500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-450900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-437400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5589,8 +5762,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +5848,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +5934,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,71 +6020,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275700</v>
+      </c>
+      <c r="E76" s="3">
         <v>276000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>278000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>279300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>281200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>277300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>275200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>163900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>160400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>161500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>157200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>145000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>89900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>96000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>110000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>123200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>138200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>150900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-313400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-301900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5921,8 +6106,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,82 +6192,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,77 +6283,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6175,8 +6369,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,19 +6403,20 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
@@ -6227,7 +6425,7 @@
         <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
@@ -6272,11 +6470,11 @@
         <v>1000</v>
       </c>
       <c r="X83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6289,8 +6487,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6573,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6659,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6745,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +6831,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,77 +6917,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6787,8 +7003,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,77 +7037,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-400</v>
       </c>
       <c r="S91" s="3">
         <v>-400</v>
       </c>
       <c r="T91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-500</v>
       </c>
       <c r="W91" s="3">
         <v>-500</v>
       </c>
       <c r="X91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6901,8 +7121,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7207,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,77 +7293,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-115600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>17300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-48400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>14100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>14900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-80200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>19200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>14500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7150,8 +7379,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,8 +7413,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7219,8 +7452,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7264,8 +7497,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7583,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7669,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,77 +7755,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>111500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>65300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>120500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>24300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,8 +7841,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7658,14 +7906,14 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
@@ -7679,77 +7927,80 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11300</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-7700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>23000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-43700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7760,6 +8011,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RXST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>RXST</t>
   </si>
@@ -656,115 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -777,80 +778,83 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E8" s="3">
         <v>32600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>37900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,79 +867,82 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E9" s="3">
         <v>7300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2400</v>
-      </c>
-      <c r="X9" s="3">
-        <v>3500</v>
       </c>
       <c r="Y9" s="3">
         <v>3500</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
+      <c r="Z9" s="3">
+        <v>3500</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
@@ -949,80 +956,83 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E10" s="3">
         <v>25300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>28300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1035,8 +1045,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1067,80 +1080,81 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E12" s="3">
         <v>8900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5300</v>
-      </c>
-      <c r="V12" s="3">
-        <v>6600</v>
       </c>
       <c r="W12" s="3">
         <v>6600</v>
       </c>
       <c r="X12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>5300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5700</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,8 +1167,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1239,8 +1256,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1268,18 +1288,18 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1295,8 +1315,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1325,34 +1345,37 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
       </c>
       <c r="H15" s="3">
+        <v>800</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1100</v>
       </c>
       <c r="L15" s="3">
         <v>1100</v>
@@ -1361,13 +1384,13 @@
         <v>1100</v>
       </c>
       <c r="N15" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="O15" s="3">
         <v>1000</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1396,8 +1419,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
@@ -1411,8 +1434,11 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1440,80 +1466,81 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E17" s="3">
         <v>43900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13100</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,80 +1553,83 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1612,8 +1642,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1644,8 +1677,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1685,39 +1719,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>35100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>39600</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1730,80 +1764,83 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-8100</v>
       </c>
       <c r="I21" s="3">
         <v>-8100</v>
       </c>
       <c r="J21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-11700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>31800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,8 +1853,11 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1849,22 +1889,22 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1500</v>
       </c>
       <c r="P22" s="3">
         <v>1500</v>
       </c>
       <c r="Q22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R22" s="3">
         <v>1300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1100</v>
       </c>
       <c r="S22" s="3">
         <v>1100</v>
@@ -1876,19 +1916,19 @@
         <v>1100</v>
       </c>
       <c r="V22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>500</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1902,80 +1942,83 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>30700</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1988,8 +2031,11 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2026,11 +2072,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2059,8 +2105,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -2074,8 +2120,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2160,80 +2209,83 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30700</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,80 +2298,83 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2387,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2418,8 +2476,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2504,8 +2565,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2590,8 +2654,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2676,8 +2743,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2717,39 +2787,39 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-39600</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,80 +2832,83 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2848,8 +2921,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2934,80 +3010,83 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3020,85 +3099,88 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3111,8 +3193,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3143,8 +3228,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3175,74 +3261,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E41" s="3">
         <v>19900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>16700</v>
       </c>
       <c r="I41" s="3">
         <v>16700</v>
       </c>
       <c r="J41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="K41" s="3">
         <v>24400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>41700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3261,74 +3348,77 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200300</v>
+      </c>
+      <c r="E42" s="3">
         <v>208200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>197900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>187100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>201300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>220500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>220400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>208800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>117500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>122000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>138300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>142900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>94000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>103900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>104600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>119700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>135000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>100000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>20000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>40000</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,74 +3437,77 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E43" s="3">
         <v>23400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3433,74 +3526,77 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E44" s="3">
         <v>31600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>29000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>9400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>9800</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3519,8 +3615,11 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3560,33 +3659,33 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,74 +3704,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>279200</v>
+      </c>
+      <c r="E46" s="3">
         <v>287500</v>
-      </c>
-      <c r="E46" s="3">
-        <v>283900</v>
       </c>
       <c r="F46" s="3">
         <v>283900</v>
       </c>
       <c r="G46" s="3">
+        <v>283900</v>
+      </c>
+      <c r="H46" s="3">
         <v>288400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>293800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>286800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>281200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>168600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>168400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>167900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>180400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>187700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>134600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>139200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>149900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>161100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>176300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>186300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>75500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>77800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3691,8 +3793,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3732,8 +3837,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3777,8 +3882,11 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3786,65 +3894,65 @@
         <v>23000</v>
       </c>
       <c r="E48" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F48" s="3">
         <v>23400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>17900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3971,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3949,8 +4060,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4035,8 +4149,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4121,13 +4238,16 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="E52" s="3">
         <v>1300</v>
@@ -4136,59 +4256,59 @@
         <v>1300</v>
       </c>
       <c r="G52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1500</v>
       </c>
       <c r="P52" s="3">
         <v>1500</v>
       </c>
       <c r="Q52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>900</v>
       </c>
       <c r="T52" s="3">
         <v>900</v>
       </c>
       <c r="U52" s="3">
+        <v>900</v>
+      </c>
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,8 +4327,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4293,74 +4416,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E54" s="3">
         <v>311800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>308500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>309000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>313000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>318600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>310500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>305500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>183200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>182600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>181900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>195300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>202500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>150200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>155700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>166700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>192700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>203700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>94900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4379,8 +4505,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4411,8 +4540,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4443,74 +4573,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5100</v>
       </c>
       <c r="K57" s="3">
         <v>5100</v>
       </c>
       <c r="L57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1700</v>
       </c>
       <c r="U57" s="3">
         <v>1700</v>
       </c>
       <c r="V57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W57" s="3">
         <v>2300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,40 +4660,43 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1100</v>
       </c>
       <c r="G58" s="3">
         <v>1100</v>
       </c>
       <c r="H58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I58" s="3">
         <v>1000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>700</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
       </c>
       <c r="K58" s="3">
+        <v>700</v>
+      </c>
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2000</v>
       </c>
       <c r="N58" s="3">
         <v>2000</v>
@@ -4571,19 +4705,19 @@
         <v>2000</v>
       </c>
       <c r="P58" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4594,8 +4728,8 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4615,74 +4749,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>9300</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>5900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>4600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>14500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4701,74 +4838,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E60" s="3">
         <v>26300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,74 +4927,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E61" s="3">
         <v>9900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>40200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>40100</v>
-      </c>
-      <c r="R61" s="3">
-        <v>40000</v>
       </c>
       <c r="S61" s="3">
         <v>40000</v>
       </c>
       <c r="T61" s="3">
+        <v>40000</v>
+      </c>
+      <c r="U61" s="3">
         <v>39800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4873,8 +5016,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4890,20 +5036,20 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>100</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
@@ -4911,36 +5057,36 @@
       <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="O62" s="3">
+        <v>100</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,8 +5105,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5045,8 +5194,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5131,8 +5283,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5217,74 +5372,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E66" s="3">
         <v>36100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>56700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>54500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>52800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>44900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5303,8 +5461,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5335,8 +5496,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5421,8 +5583,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5507,8 +5672,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5567,13 +5735,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>353300</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>353300</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>353300</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5593,8 +5761,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5679,74 +5850,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-676900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-661000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-651900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-642100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-630300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-622100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-616200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-609800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-603700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-594600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-585500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-573000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-559200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-546000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-530400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-513600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-496900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-479300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-463500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-450900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-437400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5765,8 +5939,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5851,8 +6028,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5937,8 +6117,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6023,74 +6206,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>267300</v>
+      </c>
+      <c r="E76" s="3">
         <v>275700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>276000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>278000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>279300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>281200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>277300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>275200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>163900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>160400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>161500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>157200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>145000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>89900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>96000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>110000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>123200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>138200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>150900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-313400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-301900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6295,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6195,85 +6384,88 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6286,80 +6478,83 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6372,8 +6567,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6404,22 +6602,23 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1100</v>
@@ -6428,7 +6627,7 @@
         <v>1100</v>
       </c>
       <c r="J83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -6473,11 +6672,11 @@
         <v>1000</v>
       </c>
       <c r="Y83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6689,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6576,8 +6778,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6662,8 +6867,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6748,8 +6956,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6834,8 +7045,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6920,80 +7134,83 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7006,8 +7223,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7038,80 +7258,81 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-400</v>
       </c>
       <c r="T91" s="3">
         <v>-400</v>
       </c>
       <c r="U91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-500</v>
       </c>
       <c r="X91" s="3">
         <v>-500</v>
       </c>
       <c r="Y91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7124,8 +7345,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7210,8 +7434,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7296,80 +7523,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>20900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>17300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>14100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>14900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>19200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>14500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6400</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7382,8 +7612,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7414,8 +7647,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7455,8 +7689,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7500,8 +7734,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7586,8 +7823,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7672,8 +7912,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7758,80 +8001,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>111500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>65300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>120500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>10200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>24300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7844,8 +8090,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7909,14 +8158,14 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
@@ -7930,80 +8179,83 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-7700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-43700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>26500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8014,6 +8266,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
